--- a/Zinc/6. Sensitivity analyses/Plots of HA SA/HA_Sensitivity_Summary.xlsx
+++ b/Zinc/6. Sensitivity analyses/Plots of HA SA/HA_Sensitivity_Summary.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t xml:space="preserve">Typology</t>
   </si>
@@ -58,12 +58,6 @@
   </si>
   <si>
     <t xml:space="preserve">50-60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60-70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70-80</t>
   </si>
   <si>
     <t xml:space="preserve">NP Tribs</t>
@@ -577,86 +571,86 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.00000000574640920364615</v>
+        <v>-0.000000181067108736726</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00000000204685380329114</v>
+        <v>0.0000000427953293431346</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.90554479817032</v>
+        <v>-10.4071298743988</v>
       </c>
       <c r="F7" t="n">
-        <v>0.15002104401942</v>
+        <v>1.29831285102878</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.00841904002372826</v>
+        <v>-0.0483198277403416</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00066035638255519</v>
+        <v>0.006297912891272</v>
       </c>
       <c r="I7" t="n">
-        <v>127</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.00000000504413206083846</v>
+        <v>-0.000000148892763486101</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00000000206294018107958</v>
+        <v>0.0000000361348361355586</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.84477939130903</v>
+        <v>-9.46423549319064</v>
       </c>
       <c r="F8" t="n">
-        <v>0.14528174485513</v>
+        <v>1.10796295916531</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.00814604876755622</v>
+        <v>-0.0436012239485783</v>
       </c>
       <c r="H8" t="n">
-        <v>0.000638897234964309</v>
+        <v>0.00530225479579768</v>
       </c>
       <c r="I8" t="n">
-        <v>127</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.000000181067108736726</v>
+        <v>-0.000000124502054474001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0000000427953293431346</v>
+        <v>0.000000030765410538307</v>
       </c>
       <c r="E9" t="n">
-        <v>-10.4071298743988</v>
+        <v>-8.66502238288359</v>
       </c>
       <c r="F9" t="n">
-        <v>1.29831285102878</v>
+        <v>0.956719278677838</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0483198277403416</v>
+        <v>-0.0396708223807396</v>
       </c>
       <c r="H9" t="n">
-        <v>0.006297912891272</v>
+        <v>0.0045297259644983</v>
       </c>
       <c r="I9" t="n">
         <v>14</v>
@@ -664,28 +658,28 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.000000148892763486101</v>
+        <v>-0.000000105542841467776</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0000000361348361355586</v>
+        <v>0.0000000263209279062287</v>
       </c>
       <c r="E10" t="n">
-        <v>-9.46423549319064</v>
+        <v>-7.98276948083514</v>
       </c>
       <c r="F10" t="n">
-        <v>1.10796295916531</v>
+        <v>0.835568777425311</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0436012239485783</v>
+        <v>-0.0363619084284535</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00530225479579768</v>
+        <v>0.00392217329418756</v>
       </c>
       <c r="I10" t="n">
         <v>14</v>
@@ -693,28 +687,28 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.000000124502054474001</v>
+        <v>-0.0000000905623403548146</v>
       </c>
       <c r="D11" t="n">
-        <v>0.000000030765410538307</v>
+        <v>0.0000000226401748742812</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.66502238288359</v>
+        <v>-7.39603429993522</v>
       </c>
       <c r="F11" t="n">
-        <v>0.956719278677838</v>
+        <v>0.737217911793642</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0396708223807396</v>
+        <v>-0.0335478572508133</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0045297259644983</v>
+        <v>0.00343626741145825</v>
       </c>
       <c r="I11" t="n">
         <v>14</v>
@@ -722,144 +716,144 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.000000105542841467776</v>
+        <v>-0.0000000258243511074335</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0000000263209279062287</v>
+        <v>0.0000000024132528060123</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.98276948083514</v>
+        <v>-5.28683784850436</v>
       </c>
       <c r="F12" t="n">
-        <v>0.835568777425311</v>
+        <v>0.2531997629786</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0363619084284535</v>
+        <v>-0.0237413060946953</v>
       </c>
       <c r="H12" t="n">
-        <v>0.00392217329418756</v>
+        <v>0.00116753908746925</v>
       </c>
       <c r="I12" t="n">
-        <v>14</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.0000000905623403548146</v>
+        <v>-0.0000000229064289054122</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0000000226401748742812</v>
+        <v>0.000000002148497537245</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.39603429993522</v>
+        <v>-4.98098623724192</v>
       </c>
       <c r="F13" t="n">
-        <v>0.737217911793642</v>
+        <v>0.227689860821887</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0335478572508133</v>
+        <v>-0.0223109719840559</v>
       </c>
       <c r="H13" t="n">
-        <v>0.00343626741145825</v>
+        <v>0.00104425771104331</v>
       </c>
       <c r="I13" t="n">
-        <v>14</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.0000000784959802738402</v>
+        <v>-0.0000000205020282575128</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0000000195497581171332</v>
+        <v>0.00000000194360840977778</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.88662497731242</v>
+        <v>-4.71008054828614</v>
       </c>
       <c r="F14" t="n">
-        <v>0.656454580997065</v>
+        <v>0.206793182653605</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0311270322938484</v>
+        <v>-0.0210524816134544</v>
       </c>
       <c r="H14" t="n">
-        <v>0.00304210744162073</v>
+        <v>0.000944256848700376</v>
       </c>
       <c r="I14" t="n">
-        <v>14</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.0000000686435092144021</v>
+        <v>-0.0000000184922677248421</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0000000169619456068788</v>
+        <v>0.00000000177768343895694</v>
       </c>
       <c r="E15" t="n">
-        <v>-6.43991875330897</v>
+        <v>-4.46879214718418</v>
       </c>
       <c r="F15" t="n">
-        <v>0.589182381453667</v>
+        <v>0.189048686619307</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0290203799444221</v>
+        <v>-0.019937301531557</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00271704383326373</v>
+        <v>0.000860117057435991</v>
       </c>
       <c r="I15" t="n">
-        <v>14</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.0000000258243511074335</v>
+        <v>-0.0000000167891275561663</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0000000024132528060123</v>
+        <v>0.00000000163906491433591</v>
       </c>
       <c r="E16" t="n">
-        <v>-5.28683784850436</v>
+        <v>-4.25232680589307</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2531997629786</v>
+        <v>0.173776581507817</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0237413060946953</v>
+        <v>-0.0189411527349432</v>
       </c>
       <c r="H16" t="n">
-        <v>0.00116753908746925</v>
+        <v>0.000788227345490521</v>
       </c>
       <c r="I16" t="n">
         <v>98</v>
@@ -867,378 +861,146 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.0000000229064289054122</v>
+        <v>-0.0000000102223104421495</v>
       </c>
       <c r="D17" t="n">
-        <v>0.000000002148497537245</v>
+        <v>0.000000000651340743945833</v>
       </c>
       <c r="E17" t="n">
-        <v>-4.98098623724192</v>
+        <v>-1.90359254289254</v>
       </c>
       <c r="F17" t="n">
-        <v>0.227689860821887</v>
+        <v>0.0915614241884089</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0223109719840559</v>
+        <v>-0.0083689846048215</v>
       </c>
       <c r="H17" t="n">
-        <v>0.00104425771104331</v>
+        <v>0.000407342481113868</v>
       </c>
       <c r="I17" t="n">
-        <v>98</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.0000000205020282575128</v>
+        <v>-0.0000000097790769227749</v>
       </c>
       <c r="D18" t="n">
-        <v>0.00000000194360840977778</v>
+        <v>0.000000000617719752759048</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.71008054828614</v>
+        <v>-1.86167281429913</v>
       </c>
       <c r="F18" t="n">
-        <v>0.206793182653605</v>
+        <v>0.0878706631536874</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0210524816134544</v>
+        <v>-0.00818165819358792</v>
       </c>
       <c r="H18" t="n">
-        <v>0.000944256848700376</v>
+        <v>0.000390524389420699</v>
       </c>
       <c r="I18" t="n">
-        <v>98</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.0000000184922677248421</v>
+        <v>-0.00000000937317173338892</v>
       </c>
       <c r="D19" t="n">
-        <v>0.00000000177768343895694</v>
+        <v>0.000000000584757971597511</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.46879214718418</v>
+        <v>-1.82106774004192</v>
       </c>
       <c r="F19" t="n">
-        <v>0.189048686619307</v>
+        <v>0.0842412826050944</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.019937301531557</v>
+        <v>-0.00800033364660763</v>
       </c>
       <c r="H19" t="n">
-        <v>0.000860117057435991</v>
+        <v>0.000374052533920698</v>
       </c>
       <c r="I19" t="n">
-        <v>98</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.0000000167891275561663</v>
+        <v>-0.00000000899547069856503</v>
       </c>
       <c r="D20" t="n">
-        <v>0.00000000163906491433591</v>
+        <v>0.000000000554933073585224</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.25232680589307</v>
+        <v>-1.78239997475297</v>
       </c>
       <c r="F20" t="n">
-        <v>0.173776581507817</v>
+        <v>0.0808800657605225</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0189411527349432</v>
+        <v>-0.0078278390834113</v>
       </c>
       <c r="H20" t="n">
-        <v>0.000788227345490521</v>
+        <v>0.000358826013341781</v>
       </c>
       <c r="I20" t="n">
-        <v>98</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.000000015329850803681</v>
+        <v>-0.00000000864305509519057</v>
       </c>
       <c r="D21" t="n">
-        <v>0.00000000152068766204532</v>
+        <v>0.000000000527805174517524</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.05700947652753</v>
+        <v>-1.74552305690573</v>
       </c>
       <c r="F21" t="n">
-        <v>0.160511884515765</v>
+        <v>0.0777594684719276</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0180456572251229</v>
+        <v>-0.00766349010979952</v>
       </c>
       <c r="H21" t="n">
-        <v>0.000726162505935787</v>
+        <v>0.000344713315851234</v>
       </c>
       <c r="I21" t="n">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-0.0000000140754384922954</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.00000000141737362526386</v>
-      </c>
-      <c r="E22" t="n">
-        <v>-3.88115126521354</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.148391677826469</v>
-      </c>
-      <c r="G22" t="n">
-        <v>-0.017241579120439</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.000669854562247699</v>
-      </c>
-      <c r="I22" t="n">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>19</v>
-      </c>
-      <c r="B23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-0.0000000102223104421495</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.000000000651340743945833</v>
-      </c>
-      <c r="E23" t="n">
-        <v>-1.90359254289254</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.0915614241884089</v>
-      </c>
-      <c r="G23" t="n">
-        <v>-0.0083689846048215</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.000407342481113868</v>
-      </c>
-      <c r="I23" t="n">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>19</v>
-      </c>
-      <c r="B24" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-0.0000000097790769227749</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.000000000617719752759048</v>
-      </c>
-      <c r="E24" t="n">
-        <v>-1.86167281429913</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.0878706631536874</v>
-      </c>
-      <c r="G24" t="n">
-        <v>-0.00818165819358792</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.000390524389420699</v>
-      </c>
-      <c r="I24" t="n">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>19</v>
-      </c>
-      <c r="B25" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-0.00000000937317173338892</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.000000000584757971597511</v>
-      </c>
-      <c r="E25" t="n">
-        <v>-1.82106774004192</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.0842412826050944</v>
-      </c>
-      <c r="G25" t="n">
-        <v>-0.00800033364660763</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.000374052533920698</v>
-      </c>
-      <c r="I25" t="n">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>19</v>
-      </c>
-      <c r="B26" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-0.00000000899547069856503</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.000000000554933073585224</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-1.78239997475297</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.0808800657605225</v>
-      </c>
-      <c r="G26" t="n">
-        <v>-0.0078278390834113</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.000358826013341781</v>
-      </c>
-      <c r="I26" t="n">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>19</v>
-      </c>
-      <c r="B27" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-0.00000000864305509519057</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.000000000527805174517524</v>
-      </c>
-      <c r="E27" t="n">
-        <v>-1.74552305690573</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.0777594684719276</v>
-      </c>
-      <c r="G27" t="n">
-        <v>-0.00766349010979952</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.000344713315851234</v>
-      </c>
-      <c r="I27" t="n">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>19</v>
-      </c>
-      <c r="B28" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-0.00000000831346793518261</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.000000000503036917734116</v>
-      </c>
-      <c r="E28" t="n">
-        <v>-1.7102960098077</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.0748552394911811</v>
-      </c>
-      <c r="G28" t="n">
-        <v>-0.00750663241634159</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.000331599377522648</v>
-      </c>
-      <c r="I28" t="n">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>19</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="n">
-        <v>-0.00000000799519021224175</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.000000000484792221181444</v>
-      </c>
-      <c r="E29" t="n">
-        <v>-1.67697015661714</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.0729681132058143</v>
-      </c>
-      <c r="G29" t="n">
-        <v>-0.00735865914106204</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.000322987199840236</v>
-      </c>
-      <c r="I29" t="n">
         <v>117</v>
       </c>
     </row>
@@ -1284,103 +1046,103 @@
         <v>9</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.00000000755124002786557</v>
+        <v>-0.00000000841362778611488</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00000000077445725557874</v>
+        <v>0.00000000091446216134893</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.05668623600532</v>
+        <v>-2.12929589251157</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0608689619963192</v>
+        <v>0.0741749791321119</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.00909927612808858</v>
+        <v>-0.00942596882106712</v>
       </c>
       <c r="G2" t="n">
-        <v>0.000268810322603565</v>
+        <v>0.000327922475835321</v>
       </c>
       <c r="H2" t="n">
-        <v>889</v>
+        <v>635</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.000000113958085429666</v>
+        <v>-0.000000130113421703884</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0000000113344315766803</v>
+        <v>0.0000000146362689064322</v>
       </c>
       <c r="D3" t="n">
-        <v>-8.17739075169497</v>
+        <v>-8.78303830624868</v>
       </c>
       <c r="E3" t="n">
-        <v>0.360465133985845</v>
+        <v>0.455536381185582</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.037378435998171</v>
+        <v>-0.0403003279497853</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0017187992714287</v>
+        <v>0.00217898252389467</v>
       </c>
       <c r="H3" t="n">
-        <v>98</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.0000000191313561210491</v>
+        <v>-0.0000000209028407102734</v>
       </c>
       <c r="C4" t="n">
-        <v>0.000000000718043214079789</v>
+        <v>0.000000000903832112389235</v>
       </c>
       <c r="D4" t="n">
-        <v>-4.51959776126439</v>
+        <v>-4.73980471742193</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0763613745443557</v>
+        <v>0.0958458416214206</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0201814929006097</v>
+        <v>-0.0211966427917412</v>
       </c>
       <c r="G4" t="n">
-        <v>0.000348976693435027</v>
+        <v>0.000438871297452501</v>
       </c>
       <c r="H4" t="n">
-        <v>686</v>
+        <v>490</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.00000000904596329135619</v>
+        <v>-0.00000000940261697841379</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00000000021375506872557</v>
+        <v>0.000000000263495482766297</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.78593175647388</v>
+        <v>-1.82285122577846</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0308773764156415</v>
+        <v>0.0377773893274269</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.00784394245651879</v>
+        <v>-0.00800846112764557</v>
       </c>
       <c r="G5" t="n">
-        <v>0.000137044543502384</v>
+        <v>0.000167781894164436</v>
       </c>
       <c r="H5" t="n">
-        <v>819</v>
+        <v>585</v>
       </c>
     </row>
   </sheetData>
